--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486931_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486931_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. ENABULELE OGUNSUYI</t>
+          <t>A. MEANA PEREZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6615</v>
+        <v>5.2733</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2228</v>
+        <v>2.3937</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4387</v>
+        <v>2.8795</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.819</v>
+        <v>3.9783</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.1428</v>
+        <v>-2.0309</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3238</v>
+        <v>6.0092</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.7331</v>
+        <v>3.9746</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.0093</v>
+        <v>-0.6161</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2763</v>
+        <v>4.5907</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.08599999999999999</v>
+        <v>0.0037</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1335</v>
+        <v>-1.4148</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0475</v>
+        <v>1.4185</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6427</v>
+        <v>0.8214</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.4374</v>
+        <v>-2.2588</v>
       </c>
       <c r="R2" t="n">
         <v>3.0801</v>
       </c>
       <c r="S2" t="n">
-        <v>4.419</v>
+        <v>0.4736</v>
       </c>
       <c r="T2" t="n">
-        <v>3.6726</v>
+        <v>0.4376</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7464</v>
+        <v>0.036</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7207</v>
+        <v>0.2402</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6982</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. MEANA PEREZ</t>
+          <t>D. RIVAS PALMER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3583</v>
+        <v>2.9352</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8048</v>
+        <v>1.2247</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5535</v>
+        <v>1.7105</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9783</v>
+        <v>-0.6485</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.0309</v>
+        <v>-1.6903</v>
       </c>
       <c r="I3" t="n">
-        <v>6.0092</v>
+        <v>1.0418</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9746</v>
+        <v>0.3609</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6161</v>
+        <v>-0.8885999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>4.5907</v>
+        <v>1.2495</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0037</v>
+        <v>-1.0094</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4148</v>
+        <v>-0.8017</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4185</v>
+        <v>-0.2077</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8214</v>
+        <v>2.0534</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2588</v>
+        <v>-0.4107</v>
       </c>
       <c r="R3" t="n">
-        <v>3.0801</v>
+        <v>2.4641</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4413</v>
+        <v>1.7705</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1513</v>
+        <v>1.2745</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2901</v>
+        <v>0.4961</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>-0.2402</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. KANDULU</t>
+          <t>V. PEREZ TOMAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.005</v>
+        <v>2.663</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1739</v>
+        <v>1.5996</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1689</v>
+        <v>1.0633</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5620000000000001</v>
+        <v>0.9241</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.6383</v>
+        <v>-2.0144</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0763</v>
+        <v>2.9385</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6949</v>
+        <v>1.676</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.055</v>
+        <v>-1.0993</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7498</v>
+        <v>2.7753</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2569</v>
+        <v>-0.7519</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5834</v>
+        <v>-0.9151</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3264</v>
+        <v>0.1632</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0267</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.2588</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0267</v>
+        <v>2.0534</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3392</v>
+        <v>0.1763</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2779</v>
+        <v>0.1742</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0613</v>
+        <v>0.002</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2012</v>
+        <v>1.7679</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2012</v>
+        <v>2.0082</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. RIVAS PALMER</t>
+          <t>M. ENABULELE OGUNSUYI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3463</v>
+        <v>2.6601</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6358</v>
+        <v>-1.66</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7105</v>
+        <v>4.3202</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6485</v>
+        <v>-2.819</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6903</v>
+        <v>-3.1428</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0418</v>
+        <v>0.3238</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3609</v>
+        <v>-2.7331</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8885999999999999</v>
+        <v>-3.0093</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2495</v>
+        <v>0.2763</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0094</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8017</v>
+        <v>-0.1335</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2077</v>
+        <v>0.0475</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0534</v>
+        <v>1.6427</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.4107</v>
+        <v>-1.4374</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4641</v>
+        <v>3.0801</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1816</v>
+        <v>2.4176</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6856</v>
+        <v>1.7897</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4961</v>
+        <v>0.6278</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2402</v>
+        <v>1.4189</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.7207</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2402</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. PEREZ TOMAS</t>
+          <t>D. KANDULU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0288</v>
+        <v>2.6131</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9061</v>
+        <v>2.8412</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1226</v>
+        <v>-0.2282</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9241</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.0144</v>
+        <v>-1.6383</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9385</v>
+        <v>1.0763</v>
       </c>
       <c r="J6" t="n">
-        <v>1.676</v>
+        <v>0.6949</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.0993</v>
+        <v>-0.055</v>
       </c>
       <c r="L6" t="n">
-        <v>2.7753</v>
+        <v>0.7498</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7519</v>
+        <v>-1.2569</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9151</v>
+        <v>-1.5834</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1632</v>
+        <v>0.3264</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2053</v>
+        <v>1.0267</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2588</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0534</v>
+        <v>1.0267</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4579</v>
+        <v>0.9472</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5192</v>
+        <v>0.9452</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0613</v>
+        <v>0.002</v>
       </c>
       <c r="V6" t="n">
-        <v>1.7679</v>
+        <v>1.2012</v>
       </c>
       <c r="W6" t="n">
-        <v>2.0082</v>
+        <v>1.2012</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8851</v>
+        <v>1.8077</v>
       </c>
       <c r="E7" t="n">
-        <v>0.129</v>
+        <v>0.0516</v>
       </c>
       <c r="F7" t="n">
         <v>1.7561</v>
@@ -1000,10 +1000,10 @@
         <v>2.4641</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8131</v>
+        <v>1.7357</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4565</v>
+        <v>1.3791</v>
       </c>
       <c r="U7" t="n">
         <v>0.3566</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8357</v>
+        <v>0.8793</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.462</v>
+        <v>-0.5666</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2977</v>
+        <v>1.4459</v>
       </c>
       <c r="G8" t="n">
         <v>0.4502</v>
@@ -1078,13 +1078,13 @@
         <v>1.2321</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3855</v>
+        <v>0.4291</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3757</v>
+        <v>0.2711</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0098</v>
+        <v>0.158</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0367</v>
+        <v>0.6362</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0785</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0418</v>
+        <v>-0.0175</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7527</v>
@@ -1156,13 +1156,13 @@
         <v>1.4374</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3053</v>
+        <v>0.9782</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1744</v>
+        <v>0.5578</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4797</v>
+        <v>0.4204</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. CLEMENT AIGBOGUN</t>
+          <t>H. SALOMON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9048</v>
+        <v>-0.5001</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2875</v>
+        <v>-1.4876</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3826</v>
+        <v>0.9875</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.104</v>
+        <v>-0.4304</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2856</v>
+        <v>0.5222</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1816</v>
+        <v>-0.9525</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3399</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8794</v>
+        <v>0.0195</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5395</v>
+        <v>-0.6974</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4438</v>
+        <v>0.2475</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1649</v>
+        <v>0.5027</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7211</v>
+        <v>-0.2552</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>-0.616</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0534</v>
+        <v>-1.2321</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0534</v>
+        <v>0.616</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3777</v>
+        <v>0.3061</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1858</v>
+        <v>0.1821</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1919</v>
+        <v>0.124</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1786</v>
+        <v>0.2402</v>
       </c>
       <c r="W10" t="n">
         <v>0.2402</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. SALOMON</t>
+          <t>K. CLEMENT AIGBOGUN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9325</v>
+        <v>-0.8167</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8014</v>
+        <v>-1.0511</v>
       </c>
       <c r="F11" t="n">
-        <v>0.869</v>
+        <v>0.2344</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4304</v>
+        <v>-0.104</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5222</v>
+        <v>-0.2856</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9525</v>
+        <v>0.1816</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.3399</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0195</v>
+        <v>0.8794</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6974</v>
+        <v>-0.5395</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2475</v>
+        <v>-0.4438</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5027</v>
+        <v>-1.1649</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2552</v>
+        <v>0.7211</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.616</v>
+        <v>-0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.2321</v>
+        <v>-2.0534</v>
       </c>
       <c r="R11" t="n">
-        <v>0.616</v>
+        <v>2.0534</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1263</v>
+        <v>0.4659</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1317</v>
+        <v>0.4222</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0054</v>
+        <v>0.0437</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2402</v>
+        <v>-1.1786</v>
       </c>
       <c r="W11" t="n">
         <v>0.2402</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6012</v>
+        <v>-0.8468</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0419</v>
+        <v>-1.1392</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4407</v>
+        <v>0.2925</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6656</v>
@@ -1390,13 +1390,13 @@
         <v>1.0267</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2964</v>
+        <v>1.0509</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2403</v>
+        <v>0.6624</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5367</v>
+        <v>0.3885</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>16.6455</v>
+        <v>17.3043</v>
       </c>
       <c r="E13" t="n">
-        <v>2.201099999999999</v>
+        <v>2.86</v>
       </c>
       <c r="F13" t="n">
-        <v>14.4443</v>
+        <v>14.4442</v>
       </c>
       <c r="G13" t="n">
         <v>-1.7896</v>
@@ -1441,19 +1441,19 @@
         <v>12.4184</v>
       </c>
       <c r="J13" t="n">
-        <v>4.924700000000001</v>
+        <v>4.9247</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.6239</v>
+        <v>-5.623900000000001</v>
       </c>
       <c r="L13" t="n">
         <v>10.5484</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.714300000000001</v>
+        <v>-6.7143</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.584099999999999</v>
+        <v>-8.584100000000001</v>
       </c>
       <c r="O13" t="n">
         <v>1.8697</v>
@@ -1468,10 +1468,10 @@
         <v>20.5341</v>
       </c>
       <c r="S13" t="n">
-        <v>10.0923</v>
+        <v>10.7511</v>
       </c>
       <c r="T13" t="n">
-        <v>7.4372</v>
+        <v>8.0959</v>
       </c>
       <c r="U13" t="n">
         <v>2.6551</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9416</v>
+        <v>1.8534</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7188</v>
+        <v>2.2418</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7772</v>
+        <v>-0.3884</v>
       </c>
       <c r="G14" t="n">
         <v>3.0879</v>
@@ -1546,13 +1546,13 @@
         <v>2.4641</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.3172</v>
+        <v>-1.4054</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1198</v>
+        <v>-0.5968</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1973</v>
+        <v>-0.8086</v>
       </c>
       <c r="V14" t="n">
         <v>-0.0345</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. NVE MALEVA</t>
+          <t>E. ORTIZ TORRES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1426</v>
+        <v>0.182</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1254</v>
+        <v>-0.8095</v>
       </c>
       <c r="F15" t="n">
-        <v>0.268</v>
+        <v>0.9915</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0853</v>
+        <v>-0.3194</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5508</v>
+        <v>0.7301</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4655</v>
+        <v>-1.0495</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0793</v>
+        <v>0.2638</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4084</v>
+        <v>0.2244</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6709000000000001</v>
+        <v>0.0395</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.994</v>
+        <v>-0.5833</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1425</v>
+        <v>0.5057</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1365</v>
+        <v>-1.089</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.4374</v>
+        <v>1.4374</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.0801</v>
+        <v>-1.2321</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6427</v>
+        <v>2.6694</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3243</v>
+        <v>-0.2896</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.1587</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4488</v>
+        <v>-0.4483</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.8295</v>
+        <v>-0.6464</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8295</v>
+        <v>-0.6464</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. ORTIZ TORRES</t>
+          <t>M. ALVAREZ PUERTAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.1156</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4957</v>
+        <v>0.6856</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5051</v>
+        <v>-0.57</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3194</v>
+        <v>2.2543</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7301</v>
+        <v>3.7984</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0495</v>
+        <v>-1.5442</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2638</v>
+        <v>2.282</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2244</v>
+        <v>2.9004</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0395</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5833</v>
+        <v>-0.0277</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5057</v>
+        <v>0.898</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.089</v>
+        <v>-0.9257</v>
       </c>
       <c r="P16" t="n">
-        <v>1.4374</v>
+        <v>0.4107</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.2321</v>
       </c>
       <c r="R16" t="n">
-        <v>2.6694</v>
+        <v>1.6427</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4622</v>
+        <v>-1.2048</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4725</v>
+        <v>-0.3643</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9347</v>
+        <v>-0.8405</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6464</v>
+        <v>-1.3445</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6464</v>
+        <v>-1.3445</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. AKINWOLE</t>
+          <t>C. HENDERSON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.041</v>
+        <v>-0.3203</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0341</v>
+        <v>-1.3452</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0752</v>
+        <v>1.0249</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4817</v>
+        <v>1.0708</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1603</v>
+        <v>1.4627</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.6786</v>
+        <v>-0.392</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4833</v>
+        <v>1.1306</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6546</v>
+        <v>1.0122</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1713</v>
+        <v>0.1184</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0017</v>
+        <v>-0.0599</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5057</v>
+        <v>0.4505</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5074</v>
+        <v>-0.5104</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.8214</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2588</v>
+        <v>-2.0534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4374</v>
+        <v>0.8214</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2987</v>
+        <v>-0.6169</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8096</v>
+        <v>-0.4224</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5109</v>
+        <v>-0.1946</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.4579</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. ALVAREZ PUERTAS</t>
+          <t>A. AKINWOLE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4632</v>
+        <v>-0.4995</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2672</v>
+        <v>-0.5935</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7304</v>
+        <v>0.094</v>
       </c>
       <c r="G18" t="n">
-        <v>2.2543</v>
+        <v>0.4817</v>
       </c>
       <c r="H18" t="n">
-        <v>3.7984</v>
+        <v>2.1603</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5442</v>
+        <v>-1.6786</v>
       </c>
       <c r="J18" t="n">
-        <v>2.282</v>
+        <v>1.4833</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9004</v>
+        <v>1.6546</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.1713</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0277</v>
+        <v>-1.0017</v>
       </c>
       <c r="N18" t="n">
-        <v>0.898</v>
+        <v>0.5057</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9257</v>
+        <v>-1.5074</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4107</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.2321</v>
+        <v>-2.2588</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6427</v>
+        <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.7836</v>
+        <v>-0.1598</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7827</v>
+        <v>0.182</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0009</v>
+        <v>-0.3418</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.3445</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3445</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. HENDERSON</t>
+          <t>P. ARRIBAS GOMEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4964</v>
+        <v>-0.5615</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4498</v>
+        <v>-0.9219000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9534</v>
+        <v>0.3604</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0708</v>
+        <v>-0.2661</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4627</v>
+        <v>0.2918</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.392</v>
+        <v>-0.5579</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1306</v>
+        <v>-0.6584</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0122</v>
+        <v>0.0389</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1184</v>
+        <v>-0.6974</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0599</v>
+        <v>0.3923</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4505</v>
+        <v>0.2528</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5104</v>
+        <v>0.1395</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.2321</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8214</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.793</v>
+        <v>-0.2954</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.527</v>
+        <v>-0.2635</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.266</v>
+        <v>-0.0319</v>
       </c>
       <c r="V19" t="n">
-        <v>0.4579</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.4579</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. ARRIBAS GOMEZ</t>
+          <t>J. NVE MALEVA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7097</v>
+        <v>-0.7012</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9219000000000001</v>
+        <v>-0.753</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2122</v>
+        <v>0.0518</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2661</v>
+        <v>1.0853</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2918</v>
+        <v>1.5508</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5579</v>
+        <v>-0.4655</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6584</v>
+        <v>2.0793</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0389</v>
+        <v>1.4084</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6974</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3923</v>
+        <v>-0.994</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2528</v>
+        <v>0.1425</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1395</v>
+        <v>-1.1365</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.6427</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4436</v>
+        <v>0.4804</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2635</v>
+        <v>0.2478</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1801</v>
+        <v>0.2326</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.8295</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9184</v>
+        <v>-1.1015</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3216</v>
+        <v>-1.6354</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4032</v>
+        <v>0.5339</v>
       </c>
       <c r="G21" t="n">
         <v>1.3965</v>
@@ -2092,13 +2092,13 @@
         <v>1.2321</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5327</v>
+        <v>-0.7158</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0931</v>
+        <v>-0.4069</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4396</v>
+        <v>-0.3088</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9609</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.4569</v>
+        <v>-6.3917</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.3195</v>
+        <v>-5.9011</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1374</v>
+        <v>-0.4906</v>
       </c>
       <c r="G22" t="n">
         <v>-3.8363</v>
@@ -2170,13 +2170,13 @@
         <v>2.2588</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.6333</v>
+        <v>-1.5681</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1121</v>
+        <v>-0.6937</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.5212</v>
+        <v>-0.8744</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1659</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.6535</v>
+        <v>-6.4313</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.8306</v>
+        <v>-5.4122</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8229</v>
+        <v>-1.0191</v>
       </c>
       <c r="G23" t="n">
         <v>-3.165</v>
@@ -2248,13 +2248,13 @@
         <v>1.2321</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.7496</v>
+        <v>-1.5275</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9145</v>
+        <v>-0.4961</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.8352</v>
+        <v>-1.0314</v>
       </c>
       <c r="V23" t="n">
         <v>0.3146</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-16.6456</v>
+        <v>-13.856</v>
       </c>
       <c r="E24" t="n">
         <v>-14.4444</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.2012</v>
+        <v>0.5883999999999998</v>
       </c>
       <c r="G24" t="n">
         <v>1.789700000000001</v>
@@ -2308,7 +2308,7 @@
         <v>-1.8699</v>
       </c>
       <c r="M24" t="n">
-        <v>-4.924799999999999</v>
+        <v>-4.9248</v>
       </c>
       <c r="N24" t="n">
         <v>5.623799999999999</v>
@@ -2320,19 +2320,19 @@
         <v>-5.133699999999999</v>
       </c>
       <c r="Q24" t="n">
-        <v>-20.53429999999999</v>
+        <v>-20.5343</v>
       </c>
       <c r="R24" t="n">
         <v>15.4007</v>
       </c>
       <c r="S24" t="n">
-        <v>-10.0922</v>
+        <v>-7.3029</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.6551</v>
+        <v>-2.6552</v>
       </c>
       <c r="U24" t="n">
-        <v>-7.437100000000001</v>
+        <v>-4.6477</v>
       </c>
       <c r="V24" t="n">
         <v>-3.2092</v>
